--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83173</v>
+        <v>83341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Daniella Andersson</t>
+          <t>Håkan Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
